--- a/public/data/预算汇总模板.xlsx
+++ b/public/data/预算汇总模板.xlsx
@@ -1547,15 +1547,9 @@
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3">
-        <v>100</v>
-      </c>
-      <c r="D3" s="3">
-        <v>200</v>
-      </c>
-      <c r="E3" s="3">
-        <v>300</v>
-      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
